--- a/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_los_lagos.xlsx
+++ b/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_los_lagos.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet name="Total_Regional" sheetId="1" r:id="rId1"/>
     <sheet name="Por_Sexo" sheetId="2" r:id="rId2"/>
-    <sheet name="Por_Edad" sheetId="3" r:id="rId3"/>
+    <sheet name="Por_Prov" sheetId="3" r:id="rId3"/>
+    <sheet name="Por_Edad" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -353,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -364,19 +365,44 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Residentes</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Proyectada</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Cobertura</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Categoria_lbl</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Total
-Regional</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B2">
+        <v>964999</v>
+      </c>
+      <c r="C2">
+        <v>912171</v>
+      </c>
+      <c r="D2">
         <v>105.7914579612814</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -424,17 +450,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="C2">
-        <v>483553</v>
+        <v>481446</v>
       </c>
       <c r="D2">
-        <v>453413</v>
+        <v>458758</v>
       </c>
       <c r="E2">
-        <v>106.647361235783</v>
+        <v>104.945526835499</v>
       </c>
     </row>
     <row r="3">
@@ -445,17 +471,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="C3">
-        <v>481446</v>
+        <v>483553</v>
       </c>
       <c r="D3">
-        <v>458758</v>
+        <v>453413</v>
       </c>
       <c r="E3">
-        <v>104.945526835499</v>
+        <v>106.647361235783</v>
       </c>
     </row>
   </sheetData>
@@ -465,7 +491,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -476,7 +502,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Tramo_Edad</t>
+          <t>Provincia</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -503,17 +529,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0-14</t>
+          <t>Palena</t>
         </is>
       </c>
       <c r="C2">
-        <v>156553</v>
+        <v>23026</v>
       </c>
       <c r="D2">
-        <v>165246</v>
+        <v>19402</v>
       </c>
       <c r="E2">
-        <v>94.73935829006452</v>
+        <v>118.6784867539429</v>
       </c>
     </row>
     <row r="3">
@@ -524,17 +550,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>15-29</t>
+          <t>Chiloé</t>
         </is>
       </c>
       <c r="C3">
-        <v>198396</v>
+        <v>201577</v>
       </c>
       <c r="D3">
-        <v>175241</v>
+        <v>183915</v>
       </c>
       <c r="E3">
-        <v>113.2132320632729</v>
+        <v>109.6033493733518</v>
       </c>
     </row>
     <row r="4">
@@ -545,17 +571,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30-44</t>
+          <t>Osorno</t>
         </is>
       </c>
       <c r="C4">
-        <v>224998</v>
+        <v>262172</v>
       </c>
       <c r="D4">
-        <v>203963</v>
+        <v>250192</v>
       </c>
       <c r="E4">
-        <v>110.3131450312066</v>
+        <v>104.7883225682676</v>
       </c>
     </row>
     <row r="5">
@@ -566,17 +592,138 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>45-64</t>
+          <t>Llanquihue</t>
         </is>
       </c>
       <c r="C5">
-        <v>249861</v>
+        <v>478224</v>
       </c>
       <c r="D5">
-        <v>240145</v>
+        <v>458662</v>
       </c>
       <c r="E5">
-        <v>104.0458889420975</v>
+        <v>104.2650143242736</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Desagregación 1</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Tramo_Edad</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Residentes</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Proyectada</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Cobertura</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0-4</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>37680</v>
+      </c>
+      <c r="D2">
+        <v>50680</v>
+      </c>
+      <c r="E2">
+        <v>74.34885556432518</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>5-9</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>55529</v>
+      </c>
+      <c r="D3">
+        <v>54678</v>
+      </c>
+      <c r="E3">
+        <v>101.5563846519624</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>10-14</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>63344</v>
+      </c>
+      <c r="D4">
+        <v>59888</v>
+      </c>
+      <c r="E4">
+        <v>105.7707721079348</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>15-19</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>65456</v>
+      </c>
+      <c r="D5">
+        <v>59631</v>
+      </c>
+      <c r="E5">
+        <v>109.7684090489846</v>
       </c>
     </row>
     <row r="6">
@@ -587,17 +734,269 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>65+</t>
+          <t>20-24</t>
         </is>
       </c>
       <c r="C6">
-        <v>135191</v>
+        <v>63378</v>
       </c>
       <c r="D6">
-        <v>127576</v>
+        <v>54845</v>
       </c>
       <c r="E6">
-        <v>105.9689910327961</v>
+        <v>115.5583918315252</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>25-29</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>69562</v>
+      </c>
+      <c r="D7">
+        <v>60765</v>
+      </c>
+      <c r="E7">
+        <v>114.4770838476096</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>30-34</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>79896</v>
+      </c>
+      <c r="D8">
+        <v>70928</v>
+      </c>
+      <c r="E8">
+        <v>112.6438078050981</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>35-39</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>75806</v>
+      </c>
+      <c r="D9">
+        <v>67687</v>
+      </c>
+      <c r="E9">
+        <v>111.9949177833262</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>40-44</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>69296</v>
+      </c>
+      <c r="D10">
+        <v>65348</v>
+      </c>
+      <c r="E10">
+        <v>106.0415008875559</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>45-49</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>64563</v>
+      </c>
+      <c r="D11">
+        <v>65653</v>
+      </c>
+      <c r="E11">
+        <v>98.33975598982529</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>50-54</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>65542</v>
+      </c>
+      <c r="D12">
+        <v>62817</v>
+      </c>
+      <c r="E12">
+        <v>104.3379976757884</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>55-59</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>63299</v>
+      </c>
+      <c r="D13">
+        <v>60443</v>
+      </c>
+      <c r="E13">
+        <v>104.7251129163013</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>60-64</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>56457</v>
+      </c>
+      <c r="D14">
+        <v>51232</v>
+      </c>
+      <c r="E14">
+        <v>110.1987039350406</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>65-69</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>44731</v>
+      </c>
+      <c r="D15">
+        <v>42059</v>
+      </c>
+      <c r="E15">
+        <v>106.3529803371454</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>70-74</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>33084</v>
+      </c>
+      <c r="D16">
+        <v>32892</v>
+      </c>
+      <c r="E16">
+        <v>100.5837285662167</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>75-79</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>24446</v>
+      </c>
+      <c r="D17">
+        <v>22335</v>
+      </c>
+      <c r="E17">
+        <v>109.4515334676517</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>80+</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>32930</v>
+      </c>
+      <c r="D18">
+        <v>30290</v>
+      </c>
+      <c r="E18">
+        <v>108.7157477715418</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_los_lagos.xlsx
+++ b/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_los_lagos.xlsx
@@ -418,7 +418,7 @@
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Desagregación 1</t>
+          <t>region</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -497,7 +497,7 @@
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Desagregación 1</t>
+          <t>region</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Chiloé</t>
+          <t>Chiloe</t>
         </is>
       </c>
       <c r="C3">
@@ -618,7 +618,7 @@
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Desagregación 1</t>
+          <t>region</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_los_lagos.xlsx
+++ b/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_los_lagos.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t xml:space="preserve">Categoria</t>
   </si>
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 21:15</t>
+    <t xml:space="preserve">2026-08-07 07:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -60,16 +60,25 @@
     <t xml:space="preserve">Imagen asociada</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">plot_regional_cobertura_2024_los_lagos.png</t>
   </si>
   <si>
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
+    <t xml:space="preserve">Cobertura de residentes</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
+    <t xml:space="preserve">Region de Los Lagos</t>
+  </si>
+  <si>
     <t xml:space="preserve">Año</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024</t>
   </si>
   <si>
     <t xml:space="preserve">region</t>
@@ -612,23 +621,23 @@
         <v>14</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -651,10 +660,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -668,10 +677,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>481446</v>
@@ -685,10 +694,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>483553</v>
@@ -721,10 +730,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -738,10 +747,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>23026</v>
@@ -755,10 +764,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>201577</v>
@@ -772,10 +781,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>262172</v>
@@ -789,10 +798,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>478224</v>
@@ -825,10 +834,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -842,10 +851,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>37680</v>
@@ -859,10 +868,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>55529</v>
@@ -876,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>63344</v>
@@ -893,10 +902,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>65456</v>
@@ -910,10 +919,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>63378</v>
@@ -927,10 +936,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>69562</v>
@@ -944,10 +953,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>79896</v>
@@ -961,10 +970,10 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>75806</v>
@@ -978,10 +987,10 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>69296</v>
@@ -995,10 +1004,10 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>64563</v>
@@ -1012,10 +1021,10 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>65542</v>
@@ -1029,10 +1038,10 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>63299</v>
@@ -1046,10 +1055,10 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>56457</v>
@@ -1063,10 +1072,10 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>44731</v>
@@ -1080,10 +1089,10 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>33084</v>
@@ -1097,10 +1106,10 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>24446</v>
@@ -1114,10 +1123,10 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>32930</v>

--- a/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_los_lagos.xlsx
+++ b/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_los_lagos.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-07 07:13</t>
+    <t xml:space="preserve">2026-08-28 11:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -102,7 +102,7 @@
     <t xml:space="preserve">Palena</t>
   </si>
   <si>
-    <t xml:space="preserve">Chiloe</t>
+    <t xml:space="preserve">Chiloé</t>
   </si>
   <si>
     <t xml:space="preserve">Osorno</t>

--- a/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_los_lagos.xlsx
+++ b/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_los_lagos.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 11:14</t>
+    <t xml:space="preserve">2026-09-01 13:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_los_lagos.xlsx
+++ b/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_los_lagos.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-01 13:23</t>
+    <t xml:space="preserve">2026-09-06 17:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_los_lagos.xlsx
+++ b/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_los_lagos.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:19</t>
+    <t xml:space="preserve">2026-09-08 13:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
